--- a/reference/Interventions.xlsx
+++ b/reference/Interventions.xlsx
@@ -1,14 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndahi\Downloads\meal_app_v2\meal_app\reference\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C5A36D-0509-4CB5-9AAE-76AE9220024B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$C$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$66</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Z7CykLxkHEO31+Hmr+q3s2YgATHpfISgQ2Ux/tOZV/0="/>
@@ -18,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
   <si>
     <t>UniqueID</t>
   </si>
@@ -210,53 +220,69 @@
   </si>
   <si>
     <t>Capacity Building</t>
+  </si>
+  <si>
+    <t>Lakeshores / Riverbanks/dams/Fruits</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Times New Roman&quot;"/>
     </font>
   </fonts>
   <fills count="8">
@@ -264,7 +290,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -304,7 +330,13 @@
     </fill>
   </fills>
   <borders count="7">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -318,6 +350,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -330,6 +363,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -338,17 +372,22 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -357,83 +396,62 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -623,22 +641,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C932"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="12.88"/>
-    <col customWidth="1" min="3" max="3" width="47.88"/>
-    <col customWidth="1" min="4" max="15" width="8.63"/>
+    <col min="1" max="2" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="47.88671875" customWidth="1"/>
+    <col min="4" max="15" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -649,9 +667,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:3" ht="14.25" customHeight="1">
       <c r="A2" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>3</v>
@@ -660,9 +678,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" spans="1:3" ht="14.25" customHeight="1">
       <c r="A3" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>3</v>
@@ -671,9 +689,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="1:3" ht="14.25" customHeight="1">
       <c r="A4" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>6</v>
@@ -682,9 +700,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="1:3" ht="14.25" customHeight="1">
       <c r="A5" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>6</v>
@@ -693,9 +711,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="1:3" ht="14.25" customHeight="1">
       <c r="A6" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>9</v>
@@ -704,9 +722,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" spans="1:3" ht="14.25" customHeight="1">
       <c r="A7" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>9</v>
@@ -715,9 +733,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" spans="1:3" ht="14.25" customHeight="1">
       <c r="A8" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>9</v>
@@ -726,9 +744,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" spans="1:3" ht="14.25" customHeight="1">
       <c r="A9" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>9</v>
@@ -737,9 +755,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" spans="1:3" ht="14.25" customHeight="1">
       <c r="A10" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>9</v>
@@ -748,9 +766,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:3" ht="14.25" customHeight="1">
       <c r="A11" s="7">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>9</v>
@@ -759,9 +777,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:3" ht="14.25" customHeight="1">
       <c r="A12" s="7">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>9</v>
@@ -770,9 +788,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:3" ht="14.25" customHeight="1">
       <c r="A13" s="7">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>17</v>
@@ -781,9 +799,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" spans="1:3" ht="14.25" customHeight="1">
       <c r="A14" s="7">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>17</v>
@@ -792,9 +810,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:3" ht="14.25" customHeight="1">
       <c r="A15" s="7">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>17</v>
@@ -803,9 +821,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:3" ht="14.25" customHeight="1">
       <c r="A16" s="7">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>17</v>
@@ -814,9 +832,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="1:3" ht="14.25" customHeight="1">
       <c r="A17" s="7">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>17</v>
@@ -825,9 +843,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" spans="1:3" ht="14.25" customHeight="1">
       <c r="A18" s="7">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>17</v>
@@ -836,9 +854,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" spans="1:3" ht="14.25" customHeight="1">
       <c r="A19" s="7">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>17</v>
@@ -847,9 +865,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" s="7">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>17</v>
@@ -858,9 +876,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" spans="1:3" ht="14.25" customHeight="1">
       <c r="A21" s="7">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>17</v>
@@ -869,9 +887,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" s="7">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>17</v>
@@ -880,9 +898,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" s="7">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>17</v>
@@ -891,9 +909,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" spans="1:3" ht="14.25" customHeight="1">
       <c r="A24" s="7">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>17</v>
@@ -902,9 +920,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" spans="1:3" ht="14.25" customHeight="1">
       <c r="A25" s="7">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>17</v>
@@ -913,9 +931,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" s="7">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>17</v>
@@ -924,9 +942,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" spans="1:3" ht="14.25" customHeight="1">
       <c r="A27" s="7">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>17</v>
@@ -935,9 +953,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" spans="1:3" ht="14.25" customHeight="1">
       <c r="A28" s="7">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>17</v>
@@ -946,9 +964,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" s="7">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>17</v>
@@ -957,9 +975,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" s="7">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>17</v>
@@ -968,9 +986,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" s="7">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>17</v>
@@ -979,9 +997,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" s="7">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>17</v>
@@ -990,9 +1008,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" spans="1:3" ht="14.25" customHeight="1">
       <c r="A33" s="7">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>17</v>
@@ -1001,9 +1019,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" spans="1:3" ht="14.25" customHeight="1">
       <c r="A34" s="7">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>38</v>
@@ -1012,9 +1030,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" spans="1:3" ht="14.25" customHeight="1">
       <c r="A35" s="7">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>38</v>
@@ -1023,9 +1041,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" spans="1:3" ht="14.25" customHeight="1">
       <c r="A36" s="7">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>38</v>
@@ -1034,9 +1052,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
+    <row r="37" spans="1:3" ht="14.25" customHeight="1">
       <c r="A37" s="7">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>38</v>
@@ -1045,9 +1063,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38" spans="1:3" ht="14.25" customHeight="1">
       <c r="A38" s="7">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>38</v>
@@ -1056,9 +1074,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
+    <row r="39" spans="1:3" ht="14.25" customHeight="1">
       <c r="A39" s="7">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>38</v>
@@ -1067,9 +1085,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
+    <row r="40" spans="1:3" ht="14.25" customHeight="1">
       <c r="A40" s="7">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>38</v>
@@ -1078,9 +1096,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" ht="14.25" customHeight="1">
+    <row r="41" spans="1:3" ht="14.25" customHeight="1">
       <c r="A41" s="7">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>38</v>
@@ -1089,9 +1107,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" ht="14.25" customHeight="1">
+    <row r="42" spans="1:3" ht="14.25" customHeight="1">
       <c r="A42" s="7">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>38</v>
@@ -1100,9 +1118,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="43" ht="14.25" customHeight="1">
+    <row r="43" spans="1:3" ht="14.25" customHeight="1">
       <c r="A43" s="7">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>38</v>
@@ -1111,9 +1129,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" ht="14.25" customHeight="1">
+    <row r="44" spans="1:3" ht="14.25" customHeight="1">
       <c r="A44" s="7">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>38</v>
@@ -1122,9 +1140,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" ht="14.25" customHeight="1">
+    <row r="45" spans="1:3" ht="14.25" customHeight="1">
       <c r="A45" s="7">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>38</v>
@@ -1133,9 +1151,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" ht="14.25" customHeight="1">
+    <row r="46" spans="1:3" ht="14.25" customHeight="1">
       <c r="A46" s="7">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>38</v>
@@ -1144,9 +1162,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
+    <row r="47" spans="1:3" ht="14.25" customHeight="1">
       <c r="A47" s="7">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>38</v>
@@ -1155,9 +1173,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" ht="14.25" customHeight="1">
+    <row r="48" spans="1:3" ht="14.25" customHeight="1">
       <c r="A48" s="7">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>38</v>
@@ -1166,9 +1184,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" ht="14.25" customHeight="1">
+    <row r="49" spans="1:3" ht="14.25" customHeight="1">
       <c r="A49" s="7">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="B49" s="13" t="s">
         <v>38</v>
@@ -1177,9 +1195,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" ht="14.25" customHeight="1">
+    <row r="50" spans="1:3" ht="14.25" customHeight="1">
       <c r="A50" s="7">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="B50" s="13" t="s">
         <v>52</v>
@@ -1188,9 +1206,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="51" ht="14.25" customHeight="1">
+    <row r="51" spans="1:3" ht="14.25" customHeight="1">
       <c r="A51" s="7">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="B51" s="13" t="s">
         <v>52</v>
@@ -1199,9 +1217,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="52" ht="14.25" customHeight="1">
+    <row r="52" spans="1:3" ht="14.25" customHeight="1">
       <c r="A52" s="7">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="B52" s="13" t="s">
         <v>52</v>
@@ -1210,9 +1228,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="53" ht="14.25" customHeight="1">
+    <row r="53" spans="1:3" ht="14.25" customHeight="1">
       <c r="A53" s="7">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="B53" s="13" t="s">
         <v>52</v>
@@ -1221,9 +1239,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" ht="14.25" customHeight="1">
+    <row r="54" spans="1:3" ht="14.25" customHeight="1">
       <c r="A54" s="7">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="B54" s="13" t="s">
         <v>52</v>
@@ -1232,9 +1250,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" ht="14.25" customHeight="1">
+    <row r="55" spans="1:3" ht="14.25" customHeight="1">
       <c r="A55" s="7">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="B55" s="13" t="s">
         <v>52</v>
@@ -1243,9 +1261,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" ht="14.25" customHeight="1">
+    <row r="56" spans="1:3" ht="14.25" customHeight="1">
       <c r="A56" s="7">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="B56" s="13" t="s">
         <v>52</v>
@@ -1254,9 +1272,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" ht="14.25" customHeight="1">
+    <row r="57" spans="1:3" ht="14.25" customHeight="1">
       <c r="A57" s="7">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="B57" s="13" t="s">
         <v>52</v>
@@ -1265,9 +1283,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" ht="14.25" customHeight="1">
+    <row r="58" spans="1:3" ht="14.25" customHeight="1">
       <c r="A58" s="7">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="B58" s="13" t="s">
         <v>52</v>
@@ -1276,9 +1294,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" ht="14.25" customHeight="1">
+    <row r="59" spans="1:3" ht="14.25" customHeight="1">
       <c r="A59" s="7">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="B59" s="13" t="s">
         <v>52</v>
@@ -1287,9 +1305,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" ht="14.25" customHeight="1">
+    <row r="60" spans="1:3" ht="14.25" customHeight="1">
       <c r="A60" s="7">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="B60" s="13" t="s">
         <v>52</v>
@@ -1298,9 +1316,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="61" ht="14.25" customHeight="1">
+    <row r="61" spans="1:3" ht="14.25" customHeight="1">
       <c r="A61" s="7">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="B61" s="13" t="s">
         <v>52</v>
@@ -1309,9 +1327,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" ht="14.25" customHeight="1">
+    <row r="62" spans="1:3" ht="14.25" customHeight="1">
       <c r="A62" s="7">
-        <v>61.0</v>
+        <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
         <v>52</v>
@@ -1320,9 +1338,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" ht="14.25" customHeight="1">
+    <row r="63" spans="1:3" ht="14.25" customHeight="1">
       <c r="A63" s="7">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="B63" s="13" t="s">
         <v>52</v>
@@ -1331,9 +1349,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="64" ht="14.25" customHeight="1">
+    <row r="64" spans="1:3" ht="14.25" customHeight="1">
       <c r="A64" s="7">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="B64" s="13" t="s">
         <v>38</v>
@@ -1342,9 +1360,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="65" ht="14.25" customHeight="1">
+    <row r="65" spans="1:3" ht="14.25" customHeight="1">
       <c r="A65" s="7">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="B65" s="13" t="s">
         <v>17</v>
@@ -1353,9 +1371,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="66" ht="14.25" customHeight="1">
+    <row r="66" spans="1:3" ht="14.25" customHeight="1">
       <c r="A66" s="7">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="B66" s="13" t="s">
         <v>9</v>
@@ -1364,20 +1382,30 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" ht="14.25" customHeight="1"/>
-    <row r="68" ht="14.25" customHeight="1"/>
-    <row r="69" ht="14.25" customHeight="1"/>
-    <row r="70" ht="14.25" customHeight="1"/>
-    <row r="71" ht="14.25" customHeight="1"/>
-    <row r="72" ht="14.25" customHeight="1"/>
-    <row r="73" ht="14.25" customHeight="1"/>
-    <row r="74" ht="14.25" customHeight="1"/>
-    <row r="75" ht="14.25" customHeight="1"/>
-    <row r="76" ht="14.25" customHeight="1"/>
-    <row r="77" ht="14.25" customHeight="1"/>
-    <row r="78" ht="14.25" customHeight="1"/>
-    <row r="79" ht="14.25" customHeight="1"/>
-    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="67" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A67" s="7">
+        <v>66</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="69" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="70" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="71" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="72" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="73" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="74" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="75" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="76" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="77" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="78" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="79" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="80" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="81" ht="14.25" customHeight="1"/>
     <row r="82" ht="14.25" customHeight="1"/>
     <row r="83" ht="14.25" customHeight="1"/>
@@ -2231,14 +2259,8 @@
     <row r="931" ht="14.25" customHeight="1"/>
     <row r="932" ht="14.25" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$C$66">
-    <sortState ref="A1:C66">
-      <sortCondition ref="B1:B66"/>
-    </sortState>
-  </autoFilter>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <autoFilter ref="A1:C66" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/reference/Interventions.xlsx
+++ b/reference/Interventions.xlsx
@@ -18,8 +18,19 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$66</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Z7CykLxkHEO31+Hmr+q3s2YgATHpfISgQ2Ux/tOZV/0="/>
     </ext>
